--- a/Assignment_1_Guru99.xlsx
+++ b/Assignment_1_Guru99.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Guru99" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>SGMAYB7_001</t>
   </si>
   <si>
     <t>Validate the login functionality</t>
@@ -71,41 +68,147 @@
     <t>Positive Test Cases</t>
   </si>
   <si>
-    <t>SGMAYB7_002</t>
-  </si>
-  <si>
-    <t>SGMAYB7_003</t>
-  </si>
-  <si>
     <t>Create of New Customer</t>
   </si>
   <si>
     <t>Edit Customer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://demo.guru99.com/V4/manager/Managerhomepage.php </t>
-  </si>
-  <si>
-    <t>Customer Name: Srinivas Ch
-Gender: Male</t>
-  </si>
-  <si>
-    <t>1. Click On New Customer
-2. Enter Customer Name
-3. Select Gender
-4. Enter The Date Of Birth
-5. Enter Address
-6. Enter City
-7. Enter Sate
-8. Enter PIN
-9. Enter Mobile Number
-10. Enter E-mail</t>
   </si>
   <si>
     <t>1. Open The Application URL
 2. Enter The User Name
 3. Enter The Password
 4.Click On Login Button</t>
+  </si>
+  <si>
+    <t>User Should be able to view
+Customer Registered Successfully!!!
+And Filled New Customer Details</t>
+  </si>
+  <si>
+    <t>User ID : mngr661096
+Password : mehymeq
+Customer Name: Srinivas Ch
+Gender: Male
+Date Of Birth: 15/Jan/1994
+Address: abcd
+City: Hyd
+State: Telangana
+PIN: 123456
+Mobile Number: 987654321
+E-mail: abdc@gmail.com
+Password: abdc@1234</t>
+  </si>
+  <si>
+    <t>User ID : mngr661096
+Password : mehymeq
+Customer Id: 56730</t>
+  </si>
+  <si>
+    <t>User Should be able to navigate to New Customer Page and able to view the Customer Registered Successfully!!!
+And Filled New Customer Details</t>
+  </si>
+  <si>
+    <t>1. Open The Application URL
+2. Enter The User Name
+3. Enter The Password
+4. Click On Login Button
+5. Click On New Customer
+6. Enter The Customer Name
+7. Select Gender
+8. Enter The Date Of Birth
+9. Enter The Address
+10. Enter The City
+11. Enter The Sate
+12. Enter The PIN
+13. Enter The Mobile Number
+14. Enter The E-mail
+15. Enter The Password
+16. Click On Submit Button</t>
+  </si>
+  <si>
+    <t>1. Open The Application URL
+2. Enter The User Name
+3. Enter The Password
+4.Click On Login Button
+5. Click On Edit Customer
+6. Enter Customer ID
+7. Edit The Customer Name
+8. Edit The Date Of Birth
+9. Edit The Address
+10. Edit The City
+11. Edit The State
+12. Edit The PIN
+13. Edit The Mobile Number
+14. Edit The E-mail
+15. Click On Submit Button</t>
+  </si>
+  <si>
+    <t>User Should be able to navigate to Edit Customer, able to Edit the Customer Information and able to View the updated Customer Details</t>
+  </si>
+  <si>
+    <t>Negative Test Cases</t>
+  </si>
+  <si>
+    <t>SGMAYB7+VE_001</t>
+  </si>
+  <si>
+    <t>SGMAYB7+VE_002</t>
+  </si>
+  <si>
+    <t>SGMAYB7+VE_003</t>
+  </si>
+  <si>
+    <t>SGMAYB7-VE_001</t>
+  </si>
+  <si>
+    <t>SGMAYB7-VE_002</t>
+  </si>
+  <si>
+    <t>SGMAYB7-VE_003</t>
+  </si>
+  <si>
+    <t>Test Cases Failed</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>1. Open The Application URL
+2. Enter The Invalid User Name
+3. Enter The Invalid Password
+4.Click On Login Button</t>
+  </si>
+  <si>
+    <t>User ID : mngr6610
+Password : asdfasdf</t>
+  </si>
+  <si>
+    <t>User is getting User Or Password is not valid</t>
+  </si>
+  <si>
+    <t>User ID : mngr661096
+Password : mehymeq
+Customer Name: Srinivas Ch
+Gender: Male
+Date Of Birth: 
+Address: 
+City: Hyd
+State: Telangana
+PIN: 123456
+Mobile Number: 987654321
+E-mail: abdc@gmail.com
+Password: abdc@1234</t>
+  </si>
+  <si>
+    <t>User Should be get Fill all Fields</t>
+  </si>
+  <si>
+    <t>User ID : mngr661096
+Password : mehymeq
+Customer Id: 123456</t>
+  </si>
+  <si>
+    <t>User Should get Customer does not exist!!</t>
   </si>
 </sst>
 </file>
@@ -138,7 +241,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,12 +262,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF99FF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -216,23 +325,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -242,28 +365,61 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -576,10 +732,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.85546875" customWidth="1"/>
     <col min="4" max="4" width="37.7109375" bestFit="1" customWidth="1"/>
@@ -589,132 +745,259 @@
     <col min="8" max="8" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="12"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="9"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="8"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="14"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="8"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9" ht="150" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="1:9" ht="240" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="C8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="24"/>
+    </row>
+    <row r="10" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="240" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>21</v>
+      <c r="D11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="225" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C3:C6"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="D3:D6"/>
@@ -727,8 +1010,12 @@
   <hyperlinks>
     <hyperlink ref="D3" r:id="rId1"/>
     <hyperlink ref="D7" r:id="rId2"/>
+    <hyperlink ref="D8" r:id="rId3"/>
+    <hyperlink ref="D10" r:id="rId4"/>
+    <hyperlink ref="D11" r:id="rId5"/>
+    <hyperlink ref="D12" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>